--- a/reports/telegram/aegis_daily_2026-09-04.xlsx
+++ b/reports/telegram/aegis_daily_2026-09-04.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV22"/>
+  <dimension ref="A1:AV17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -733,12 +733,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>R2-GNFC-IND-20260806-abf3d2</t>
+          <t>R2-PLTR-USA-20260810-caa9a7</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>GNFC_IND_20260806</t>
+          <t>PLTR_USA_20260810</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
@@ -775,7 +775,7 @@
       <c r="L2" s="3" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
@@ -783,24 +783,24 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>33.3</v>
+        <v>50.6</v>
       </c>
       <c r="Q2" s="3" t="n">
         <v>-0.8</v>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 34% · band HOLD→STRONG · 17d left · → STRONG BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 51% · band HOLD · 17d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr"/>
       <c r="U2" s="3" t="n">
-        <v>34.1</v>
+        <v>51.4</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -808,13 +808,13 @@
         </is>
       </c>
       <c r="W2" s="3" t="n">
-        <v>36</v>
+        <v>33.8</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Z2" s="3" t="n">
         <v>17</v>
@@ -824,57 +824,57 @@
       </c>
       <c r="AB2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="AC2" s="3" t="n">
-        <v>587.35</v>
+        <v>182.53</v>
       </c>
       <c r="AD2" s="3" t="n">
-        <v>553.3</v>
+        <v>182.53</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>581.48</v>
+        <v>180.7</v>
       </c>
       <c r="AF2" s="3" t="n">
-        <v>593.22</v>
+        <v>184.36</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>552.11</v>
+        <v>171.58</v>
       </c>
       <c r="AH2" s="3" t="n">
-        <v>-0.22</v>
+        <v>-6</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>657.83</v>
+        <v>204.43</v>
       </c>
       <c r="AJ2" s="3" t="n">
-        <v>18.89</v>
+        <v>12</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>728.3099999999999</v>
+        <v>226.34</v>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>31.63</v>
+        <v>24</v>
       </c>
       <c r="AM2" s="3" t="n">
-        <v>576.95</v>
+        <v>169.46</v>
       </c>
       <c r="AN2" s="3" t="n">
-        <v>1.8</v>
+        <v>7.71</v>
       </c>
       <c r="AO2" s="3" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="AP2" s="3" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="AQ2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Value · Momentum · Trend</t>
+          <t>Value · Quality · Growth</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr"/>
@@ -886,19 +886,19 @@
       </c>
       <c r="AV2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 00:46</t>
+          <t>2026-09-04 12:28</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>R2-LICI-IND-20260805-a4f409</t>
+          <t>R2-COP-USA-20260904-01ae27</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>LICI_IND_20260805</t>
+          <t>COP_USA_20260904</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -929,19 +929,19 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>→ GNFC.NS · +17.1pp alpha</t>
+          <t>→ PLTR · +5.5pp alpha</t>
         </is>
       </c>
       <c r="J3" s="3" t="n">
-        <v>6.54</v>
+        <v>0</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="n">
-        <v>75.09999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
@@ -949,24 +949,24 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>33.6</v>
+        <v>56.4</v>
       </c>
       <c r="Q3" s="3" t="n">
         <v>-0.8</v>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank #9 · Conf 34% · band HOLD · 60d left · → EXIT (rotate to GNFC.NS)</t>
+          <t>🔴 AVOID · Rank #6 · Conf 57% · band STRONG · 60d left · → EXIT (rotate to PLTR)</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="n">
-        <v>34.3</v>
+        <v>57.1</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="W3" s="3" t="n">
-        <v>18.9</v>
+        <v>28.3</v>
       </c>
       <c r="X3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Z3" s="3" t="n">
         <v>60</v>
@@ -990,77 +990,77 @@
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AC3" s="3" t="n">
-        <v>416.9</v>
+        <v>135.72</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>391.3</v>
+        <v>135.72</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>387.39</v>
+        <v>134.36</v>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>395.21</v>
+        <v>137.08</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>371.74</v>
+        <v>128.93</v>
       </c>
       <c r="AH3" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>422.6</v>
+        <v>146.58</v>
       </c>
       <c r="AJ3" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>450</v>
+        <v>156.08</v>
       </c>
       <c r="AL3" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" s="3" t="n">
-        <v>408.25</v>
+        <v>137.2</v>
       </c>
       <c r="AN3" s="3" t="n">
-        <v>2.12</v>
+        <v>-1.08</v>
       </c>
       <c r="AO3" s="3" t="inlineStr"/>
       <c r="AP3" s="3" t="n">
-        <v>6.54</v>
+        <v>0</v>
       </c>
       <c r="AQ3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Value · Momentum · Mean Reversion</t>
+          <t>Trend · Momentum · News</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr"/>
       <c r="AT3" s="3" t="inlineStr"/>
       <c r="AU3" s="3" t="n">
-        <v>17.11</v>
+        <v>5.49</v>
       </c>
       <c r="AV3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 00:46</t>
+          <t>2026-09-04 12:28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>R1-ICICIBANK-IND-20260904-9d8bde</t>
+          <t>R2-PSX-USA-20260904-1d95f1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ICICIBANK_IND_20260904</t>
+          <t>PSX_USA_20260904</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1070,53 +1070,65 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>ICICI Bank</t>
-        </is>
-      </c>
+          <t>PSX</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>→ PLTR · +7.3pp alpha</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N4" s="3" t="inlineStr"/>
-      <c r="O4" s="3" t="inlineStr"/>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="inlineStr"/>
-      <c r="R4" s="3" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.5%) · Rank ↑ 2→1 · Conf 84% · momentum → · 91d left · → STRONG BUY</t>
+          <t>🔴 AVOID · Rank #10 · Conf 51% · band HOLD · 60d left · → EXIT (rotate to PLTR)</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr"/>
       <c r="U4" s="3" t="n">
-        <v>84</v>
+        <v>51.4</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1124,91 +1136,93 @@
         </is>
       </c>
       <c r="W4" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="X4" s="3" t="inlineStr"/>
+        <v>26.5</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AA4" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB4" s="3" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="AC4" s="3" t="n">
-        <v>1430</v>
+        <v>254.66</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>1438.5</v>
+        <v>254.66</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>1393</v>
+        <v>252.11</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>1467</v>
+        <v>257.21</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>1358.5</v>
+        <v>241.93</v>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>-5.56</v>
+        <v>-5</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>1506</v>
+        <v>275.03</v>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>4.69</v>
+        <v>8</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>1611.42</v>
+        <v>292.86</v>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>12.02</v>
+        <v>15</v>
       </c>
       <c r="AM4" s="3" t="n">
-        <v>1426.5</v>
+        <v>256.09</v>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AO4" s="3" t="n">
-        <v>-0.59</v>
-      </c>
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="AO4" s="3" t="inlineStr"/>
       <c r="AP4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR4" s="3" t="inlineStr"/>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Trend · Momentum · Growth</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr"/>
+      <c r="AT4" s="3" t="inlineStr"/>
       <c r="AU4" s="3" t="n">
-        <v>4.69</v>
+        <v>7.33</v>
       </c>
       <c r="AV4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 00:46</t>
+          <t>2026-09-04 12:28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>R1-BEL-IND-20260904-842c9e</t>
+          <t>R2-TAP-USA-20260904-8b67a3</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>BEL_IND_20260904</t>
+          <t>TAP_USA_20260904</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1218,53 +1232,65 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>BEL</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Bharat Electronics</t>
-        </is>
-      </c>
+          <t>TAP</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>→ PLTR · +60.0pp alpha</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K5" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>-4</v>
-      </c>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.7%) · Rank ↑ 8→4 · Conf 67% · momentum → · 91d left · → BUY</t>
+          <t>🔴 AVOID · Rank #11 · Conf 31% · band EXIT · 60d left · → EXIT (rotate to PLTR)</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="n">
-        <v>67</v>
+        <v>30.9</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
@@ -1272,91 +1298,93 @@
         </is>
       </c>
       <c r="W5" s="3" t="n">
+        <v>-26.1</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="X5" s="3" t="inlineStr"/>
-      <c r="Y5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="3" t="n">
-        <v>90</v>
-      </c>
       <c r="AA5" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB5" s="3" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="AC5" s="3" t="n">
-        <v>408.6</v>
+        <v>40.57</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>388.7</v>
+        <v>40.57</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>397</v>
+        <v>40.16</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>420</v>
+        <v>40.98</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>388.17</v>
+        <v>38.54</v>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>-0.14</v>
+        <v>-5</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>441.2880000000001</v>
+        <v>43.82</v>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>13.53</v>
+        <v>8.01</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>472.1781600000001</v>
+        <v>46.66</v>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>21.48</v>
+        <v>15.01</v>
       </c>
       <c r="AM5" s="3" t="n">
-        <v>405.75</v>
+        <v>40.54</v>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AO5" s="3" t="n">
-        <v>5.12</v>
-      </c>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AO5" s="3" t="inlineStr"/>
       <c r="AP5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR5" s="3" t="inlineStr"/>
-      <c r="AS5" s="3" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="AT5" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr"/>
+      <c r="AT5" s="3" t="inlineStr"/>
       <c r="AU5" s="3" t="n">
-        <v>13.53</v>
+        <v>59.95</v>
       </c>
       <c r="AV5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 00:46</t>
+          <t>2026-09-04 12:28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>R1-ONGC-IND-20260811-f86a0f</t>
+          <t>R1-MU-USA-20260904-bcf995</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ONGC_IND_20260811</t>
+          <t>MU_USA_20260904</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1366,7 +1394,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1376,7 +1404,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr"/>
@@ -1388,23 +1416,37 @@
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L6" s="3" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr"/>
-      <c r="N6" s="3" t="inlineStr"/>
-      <c r="O6" s="3" t="inlineStr"/>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.9%) · Rank #6 · Conf 68% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #1 · Conf 51% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr"/>
       <c r="U6" s="3" t="n">
-        <v>68</v>
+        <v>51.1</v>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
@@ -1412,11 +1454,11 @@
         </is>
       </c>
       <c r="W6" s="3" t="n">
-        <v>55</v>
+        <v>68.5</v>
       </c>
       <c r="X6" s="3" t="inlineStr"/>
       <c r="Y6" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>90</v>
@@ -1424,56 +1466,56 @@
       <c r="AA6" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="AB6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
+      <c r="AB6" s="3" t="inlineStr"/>
       <c r="AC6" s="3" t="n">
-        <v>236</v>
+        <v>958.16</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>236</v>
+        <v>958.16</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>229</v>
+        <v>939</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>243</v>
+        <v>977.3200000000001</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>224.2</v>
+        <v>910.252</v>
       </c>
       <c r="AH6" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>254.88</v>
+        <v>1034.8128</v>
       </c>
       <c r="AJ6" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>272.7216</v>
+        <v>1107.249696</v>
       </c>
       <c r="AL6" s="3" t="n">
         <v>15.56</v>
       </c>
       <c r="AM6" s="3" t="n">
-        <v>237.5</v>
+        <v>956.08</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>-0.63</v>
+        <v>0.22</v>
       </c>
       <c r="AO6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AP6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR6" s="3" t="inlineStr"/>
       <c r="AS6" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT6" s="3" t="n">
@@ -1484,19 +1526,19 @@
       </c>
       <c r="AV6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 00:46</t>
+          <t>2026-09-04 12:28</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>R1-TATASTEEL-IND-20260828-9c799a</t>
+          <t>R1-PLTR-USA-20260904-ed7adc</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TATASTEEL_IND_20260828</t>
+          <t>PLTR_USA_20260904</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1506,7 +1548,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1516,7 +1558,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -1528,23 +1570,37 @@
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr"/>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.0%) · Rank #8 · Conf 64% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 51% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="n">
-        <v>64</v>
+        <v>51.4</v>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
@@ -1552,11 +1608,11 @@
         </is>
       </c>
       <c r="W7" s="3" t="n">
-        <v>53</v>
+        <v>67.3</v>
       </c>
       <c r="X7" s="3" t="inlineStr"/>
       <c r="Y7" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>90</v>
@@ -1564,79 +1620,79 @@
       <c r="AA7" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="AB7" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
+      <c r="AB7" s="3" t="inlineStr"/>
       <c r="AC7" s="3" t="n">
-        <v>184.2</v>
+        <v>182.53</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>184.1999969482422</v>
+        <v>182.53</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>179</v>
+        <v>180.7</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>190</v>
+        <v>184.36</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>174.99</v>
+        <v>173.4035</v>
       </c>
       <c r="AH7" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>198.936</v>
+        <v>204.43</v>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>212.86152</v>
+        <v>218.7401</v>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>15.56</v>
+        <v>19.84</v>
       </c>
       <c r="AM7" s="3" t="n">
-        <v>183.85</v>
+        <v>169.46</v>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>0.19</v>
+        <v>7.71</v>
       </c>
       <c r="AO7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AP7" s="3" t="inlineStr"/>
-      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AP7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR7" s="3" t="inlineStr"/>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT7" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 00:46</t>
+          <t>2026-09-04 12:28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>R1-DABUR-IND-20260828-284464</t>
+          <t>R1-INCY-USA-20260904-e82d63</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>DABUR_IND_20260828</t>
+          <t>INCY_USA_20260904</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1646,7 +1702,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1656,7 +1712,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr"/>
@@ -1668,23 +1724,37 @@
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr"/>
-      <c r="N8" s="3" t="inlineStr"/>
-      <c r="O8" s="3" t="inlineStr"/>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.1%) · Rank #9 · Conf 62% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #3 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr"/>
       <c r="U8" s="3" t="n">
-        <v>62</v>
+        <v>54.2</v>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
@@ -1692,11 +1762,11 @@
         </is>
       </c>
       <c r="W8" s="3" t="n">
-        <v>48</v>
+        <v>66.5</v>
       </c>
       <c r="X8" s="3" t="inlineStr"/>
       <c r="Y8" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>90</v>
@@ -1704,79 +1774,79 @@
       <c r="AA8" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="AB8" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
+      <c r="AB8" s="3" t="inlineStr"/>
       <c r="AC8" s="3" t="n">
-        <v>380.7</v>
+        <v>128</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>380.7000122070312</v>
+        <v>128</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>369</v>
+        <v>126.72</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>393</v>
+        <v>129.28</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>361.665</v>
+        <v>121.6</v>
       </c>
       <c r="AH8" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>411.156</v>
+        <v>143.36</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>439.93692</v>
+        <v>153.3952</v>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>15.56</v>
+        <v>19.84</v>
       </c>
       <c r="AM8" s="3" t="n">
-        <v>379</v>
+        <v>128.83</v>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>0.45</v>
+        <v>-0.64</v>
       </c>
       <c r="AO8" s="3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AP8" s="3" t="inlineStr"/>
-      <c r="AQ8" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AP8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR8" s="3" t="inlineStr"/>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT8" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU8" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 00:46</t>
+          <t>2026-09-04 12:28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>R1-IRCTC-IND-20260904-004535</t>
+          <t>R1-HOOD-USA-20260904-31b01c</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>IRCTC_IND_20260904</t>
+          <t>HOOD_USA_20260904</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1786,7 +1856,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1796,43 +1866,49 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>IRCTC</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>IRCTC</t>
-        </is>
-      </c>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="N9" s="3" t="inlineStr"/>
-      <c r="O9" s="3" t="inlineStr"/>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.8%) · Rank ↓ 7→10 · Conf 65% · momentum → · 91d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 51% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr"/>
       <c r="U9" s="3" t="n">
-        <v>65</v>
+        <v>51.4</v>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
@@ -1840,7 +1916,7 @@
         </is>
       </c>
       <c r="W9" s="3" t="n">
-        <v>48</v>
+        <v>60.9</v>
       </c>
       <c r="X9" s="3" t="inlineStr"/>
       <c r="Y9" s="3" t="n">
@@ -1854,43 +1930,43 @@
       </c>
       <c r="AB9" s="3" t="inlineStr"/>
       <c r="AC9" s="3" t="n">
-        <v>474.6</v>
+        <v>124.72</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>494.35</v>
+        <v>124.72</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>461</v>
+        <v>122.23</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>488</v>
+        <v>127.21</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>450.87</v>
+        <v>118.484</v>
       </c>
       <c r="AH9" s="3" t="n">
-        <v>-8.800000000000001</v>
+        <v>-5</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>512.5680000000001</v>
+        <v>134.6976</v>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>3.69</v>
+        <v>8</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>548.4477600000001</v>
+        <v>144.126432</v>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>10.94</v>
+        <v>15.56</v>
       </c>
       <c r="AM9" s="3" t="n">
-        <v>472.6</v>
+        <v>106.99</v>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>0.42</v>
+        <v>16.57</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="AP9" s="3" t="n">
         <v>0</v>
@@ -1901,30 +1977,30 @@
       <c r="AR9" s="3" t="inlineStr"/>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AT9" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU9" s="3" t="n">
-        <v>3.69</v>
+        <v>8</v>
       </c>
       <c r="AV9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 00:46</t>
+          <t>2026-09-04 12:28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>R2-CHAMBLFERT-IND-20260804-5eb424</t>
+          <t>R1-VLO-USA-20260904-c6a265</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CHAMBLFERT_IND_20260804</t>
+          <t>VLO_USA_20260904</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1934,53 +2010,59 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Chambal Fert.</t>
-        </is>
-      </c>
+          <t>VLO</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr"/>
       <c r="K10" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L10" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M10" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="N10" s="3" t="inlineStr"/>
-      <c r="O10" s="3" t="inlineStr"/>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 3→8 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #5 · Conf 57% · momentum → · band STRONG · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr"/>
       <c r="U10" s="3" t="n">
-        <v>38.3</v>
+        <v>57.1</v>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
@@ -1988,89 +2070,91 @@
         </is>
       </c>
       <c r="W10" s="3" t="n">
-        <v>22.4</v>
+        <v>58.6</v>
       </c>
       <c r="X10" s="3" t="inlineStr"/>
       <c r="Y10" s="3" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA10" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB10" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB10" s="3" t="inlineStr"/>
       <c r="AC10" s="3" t="n">
-        <v>443.35</v>
+        <v>370.69</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>443.35</v>
+        <v>370.69</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>438.92</v>
+        <v>366.98</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>447.78</v>
+        <v>374.4</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>421.1825</v>
+        <v>352.1555</v>
       </c>
       <c r="AH10" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>478.818</v>
+        <v>415.17</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>509.8525</v>
+        <v>444.2319000000001</v>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>15</v>
+        <v>19.84</v>
       </c>
       <c r="AM10" s="3" t="n">
-        <v>411.45</v>
+        <v>366.09</v>
       </c>
       <c r="AN10" s="3" t="n">
-        <v>1.66</v>
+        <v>1.26</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP10" s="3" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AQ10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AR10" s="3" t="inlineStr"/>
-      <c r="AS10" s="3" t="inlineStr"/>
-      <c r="AT10" s="3" t="inlineStr"/>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU10" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 00:46</t>
+          <t>2026-09-04 12:28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>R2-PNB-IND-20260804-c7957c</t>
+          <t>R1-GRMN-USA-20260904-66577b</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>PNB_IND_20260804</t>
+          <t>GRMN_USA_20260904</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -2080,24 +2164,20 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Punjab Natl. Bank</t>
-        </is>
-      </c>
+          <t>GRMN</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2106,27 +2186,37 @@
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="3" t="inlineStr"/>
-      <c r="O11" s="3" t="inlineStr"/>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 32% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #6 · Conf 54% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr"/>
       <c r="U11" s="3" t="n">
-        <v>32.1</v>
+        <v>54.1</v>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
@@ -2134,58 +2224,54 @@
         </is>
       </c>
       <c r="W11" s="3" t="n">
-        <v>22.2</v>
+        <v>47.7</v>
       </c>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA11" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB11" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB11" s="3" t="inlineStr"/>
       <c r="AC11" s="3" t="n">
-        <v>113.36</v>
+        <v>277.18</v>
       </c>
       <c r="AD11" s="3" t="n">
-        <v>113.36</v>
+        <v>277.18</v>
       </c>
       <c r="AE11" s="3" t="n">
-        <v>112.23</v>
+        <v>271.64</v>
       </c>
       <c r="AF11" s="3" t="n">
-        <v>114.49</v>
+        <v>282.72</v>
       </c>
       <c r="AG11" s="3" t="n">
-        <v>107.692</v>
+        <v>263.321</v>
       </c>
       <c r="AH11" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>122.4288</v>
+        <v>299.3544000000001</v>
       </c>
       <c r="AJ11" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>130.364</v>
+        <v>320.3092080000001</v>
       </c>
       <c r="AL11" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM11" s="3" t="n">
-        <v>117</v>
+        <v>276.04</v>
       </c>
       <c r="AN11" s="3" t="n">
-        <v>-0.58</v>
+        <v>0.41</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>0</v>
@@ -2194,29 +2280,35 @@
         <v>0</v>
       </c>
       <c r="AQ11" s="3" t="n">
-        <v>-2.01</v>
+        <v>0</v>
       </c>
       <c r="AR11" s="3" t="inlineStr"/>
-      <c r="AS11" s="3" t="inlineStr"/>
-      <c r="AT11" s="3" t="inlineStr"/>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU11" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 00:46</t>
+          <t>2026-09-04 12:28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>R2-ITC-IND-20260804-a049df</t>
+          <t>R1-GDDY-USA-20260904-9a4122</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ITC_IND_20260804</t>
+          <t>GDDY_USA_20260904</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -2226,24 +2318,20 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>ITC</t>
-        </is>
-      </c>
+          <t>GDDY</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
       <c r="H12" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2252,27 +2340,37 @@
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr"/>
       <c r="K12" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L12" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="M12" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N12" s="3" t="inlineStr"/>
-      <c r="O12" s="3" t="inlineStr"/>
-      <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="inlineStr"/>
-      <c r="R12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 7→9 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 54% · momentum → · band STRONG · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr"/>
       <c r="U12" s="3" t="n">
-        <v>38.3</v>
+        <v>54.2</v>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
@@ -2280,89 +2378,91 @@
         </is>
       </c>
       <c r="W12" s="3" t="n">
-        <v>21.6</v>
+        <v>40.2</v>
       </c>
       <c r="X12" s="3" t="inlineStr"/>
       <c r="Y12" s="3" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA12" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB12" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB12" s="3" t="inlineStr"/>
       <c r="AC12" s="3" t="n">
-        <v>282.9</v>
+        <v>103.63</v>
       </c>
       <c r="AD12" s="3" t="n">
-        <v>282.9</v>
+        <v>103.63</v>
       </c>
       <c r="AE12" s="3" t="n">
-        <v>280.07</v>
+        <v>101.56</v>
       </c>
       <c r="AF12" s="3" t="n">
-        <v>285.73</v>
+        <v>105.7</v>
       </c>
       <c r="AG12" s="3" t="n">
-        <v>268.7549999999999</v>
+        <v>98.4485</v>
       </c>
       <c r="AH12" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>305.532</v>
+        <v>111.9204</v>
       </c>
       <c r="AJ12" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>325.3349999999999</v>
+        <v>119.754828</v>
       </c>
       <c r="AL12" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM12" s="3" t="n">
-        <v>266.3</v>
+        <v>101.87</v>
       </c>
       <c r="AN12" s="3" t="n">
-        <v>-1.24</v>
+        <v>1.73</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP12" s="3" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AQ12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AR12" s="3" t="inlineStr"/>
-      <c r="AS12" s="3" t="inlineStr"/>
-      <c r="AT12" s="3" t="inlineStr"/>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU12" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 00:46</t>
+          <t>2026-09-04 12:28</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>R2-BATAINDIA-IND-20260804-21b729</t>
+          <t>R1-CRM-USA-20260904-7dc69e</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>BATAINDIA_IND_20260804</t>
+          <t>CRM_USA_20260904</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -2372,22 +2472,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Bata India</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -2398,27 +2498,37 @@
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="3" t="inlineStr"/>
-      <c r="O13" s="3" t="inlineStr"/>
-      <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="3" t="inlineStr"/>
-      <c r="R13" s="3" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 15→15 · Conf 24% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 54% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr"/>
       <c r="U13" s="3" t="n">
-        <v>24</v>
+        <v>54.1</v>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
@@ -2426,58 +2536,54 @@
         </is>
       </c>
       <c r="W13" s="3" t="n">
-        <v>-30.3</v>
+        <v>36.4</v>
       </c>
       <c r="X13" s="3" t="inlineStr"/>
       <c r="Y13" s="3" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA13" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB13" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB13" s="3" t="inlineStr"/>
       <c r="AC13" s="3" t="n">
-        <v>709</v>
+        <v>264.43</v>
       </c>
       <c r="AD13" s="3" t="n">
-        <v>709</v>
+        <v>264.43</v>
       </c>
       <c r="AE13" s="3" t="n">
-        <v>701.91</v>
+        <v>259.14</v>
       </c>
       <c r="AF13" s="3" t="n">
-        <v>716.09</v>
+        <v>269.72</v>
       </c>
       <c r="AG13" s="3" t="n">
-        <v>673.55</v>
+        <v>251.2085</v>
       </c>
       <c r="AH13" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>765.72</v>
+        <v>285.5844</v>
       </c>
       <c r="AJ13" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>815.3499999999999</v>
+        <v>305.5753080000001</v>
       </c>
       <c r="AL13" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM13" s="3" t="n">
-        <v>670.45</v>
+        <v>256.93</v>
       </c>
       <c r="AN13" s="3" t="n">
-        <v>1.04</v>
+        <v>2.92</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>0</v>
@@ -2486,29 +2592,35 @@
         <v>0</v>
       </c>
       <c r="AQ13" s="3" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="AR13" s="3" t="inlineStr"/>
-      <c r="AS13" s="3" t="inlineStr"/>
-      <c r="AT13" s="3" t="inlineStr"/>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU13" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AV13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 00:46</t>
+          <t>2026-09-04 12:28</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>R2-PERSISTENT-IND-20260805-48a8e2</t>
+          <t>R1-PSX-USA-20260904-b831e4</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PERSISTENT_IND_20260805</t>
+          <t>PSX_USA_20260904</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2518,17 +2630,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -2540,27 +2652,37 @@
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr"/>
       <c r="K14" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="inlineStr"/>
-      <c r="O14" s="3" t="inlineStr"/>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 41% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 51% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr"/>
       <c r="U14" s="3" t="n">
-        <v>40.7</v>
+        <v>51.4</v>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
@@ -2568,89 +2690,91 @@
         </is>
       </c>
       <c r="W14" s="3" t="n">
-        <v>23.8</v>
+        <v>36</v>
       </c>
       <c r="X14" s="3" t="inlineStr"/>
       <c r="Y14" s="3" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA14" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB14" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB14" s="3" t="inlineStr"/>
       <c r="AC14" s="3" t="n">
-        <v>5322.4</v>
+        <v>254.66</v>
       </c>
       <c r="AD14" s="3" t="n">
-        <v>5322.4</v>
+        <v>254.66</v>
       </c>
       <c r="AE14" s="3" t="n">
-        <v>5269.18</v>
+        <v>249.57</v>
       </c>
       <c r="AF14" s="3" t="n">
-        <v>5375.62</v>
+        <v>259.75</v>
       </c>
       <c r="AG14" s="3" t="n">
-        <v>5056.28</v>
+        <v>241.927</v>
       </c>
       <c r="AH14" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>5748.192</v>
+        <v>275.0328</v>
       </c>
       <c r="AJ14" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>6120.759999999999</v>
+        <v>294.285096</v>
       </c>
       <c r="AL14" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM14" s="3" t="n">
-        <v>5690</v>
+        <v>256.09</v>
       </c>
       <c r="AN14" s="3" t="n">
-        <v>-0.58</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP14" s="3" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AQ14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AR14" s="3" t="inlineStr"/>
-      <c r="AS14" s="3" t="inlineStr"/>
-      <c r="AT14" s="3" t="inlineStr"/>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU14" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 00:46</t>
+          <t>2026-09-04 12:28</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>R2-BAJAJHLDNG-IND-20260805-660791</t>
+          <t>R1-COP-USA-20260904-e63c2d</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG_IND_20260805</t>
+          <t>COP_USA_20260904</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2660,17 +2784,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
@@ -2684,25 +2808,35 @@
       <c r="K15" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L15" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3" t="inlineStr"/>
-      <c r="O15" s="3" t="inlineStr"/>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr"/>
-      <c r="R15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 10→10 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 57% · momentum → · band STRONG · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr"/>
       <c r="U15" s="3" t="n">
-        <v>38.3</v>
+        <v>57.1</v>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
@@ -2710,89 +2844,91 @@
         </is>
       </c>
       <c r="W15" s="3" t="n">
-        <v>20.7</v>
+        <v>36</v>
       </c>
       <c r="X15" s="3" t="inlineStr"/>
       <c r="Y15" s="3" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA15" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB15" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB15" s="3" t="inlineStr"/>
       <c r="AC15" s="3" t="n">
-        <v>11127</v>
+        <v>135.72</v>
       </c>
       <c r="AD15" s="3" t="n">
-        <v>11127</v>
+        <v>135.72</v>
       </c>
       <c r="AE15" s="3" t="n">
-        <v>11015.73</v>
+        <v>133.01</v>
       </c>
       <c r="AF15" s="3" t="n">
-        <v>11238.27</v>
+        <v>138.43</v>
       </c>
       <c r="AG15" s="3" t="n">
-        <v>10570.65</v>
+        <v>128.934</v>
       </c>
       <c r="AH15" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>12017.16</v>
+        <v>146.5776</v>
       </c>
       <c r="AJ15" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>12796.05</v>
+        <v>156.838032</v>
       </c>
       <c r="AL15" s="3" t="n">
-        <v>15</v>
+        <v>15.56</v>
       </c>
       <c r="AM15" s="3" t="n">
-        <v>11310</v>
+        <v>137.2</v>
       </c>
       <c r="AN15" s="3" t="n">
-        <v>-1.86</v>
+        <v>-1.08</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP15" s="3" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="AQ15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AR15" s="3" t="inlineStr"/>
-      <c r="AS15" s="3" t="inlineStr"/>
-      <c r="AT15" s="3" t="inlineStr"/>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU15" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 00:46</t>
+          <t>2026-09-04 12:28</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>R2-TIINDIA-IND-20260805-44fbae</t>
+          <t>R2-TRV-USA-20260810-a2c57b</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>TIINDIA_IND_20260805</t>
+          <t>TRV_USA_20260810</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2802,7 +2938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2812,10 +2948,14 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr"/>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2824,10 +2964,14 @@
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="N16" s="3" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr"/>
       <c r="P16" s="3" t="inlineStr"/>
@@ -2835,12 +2979,12 @@
       <c r="R16" s="3" t="inlineStr"/>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #12 · Conf 22% · momentum → · 61d left · → HOLD</t>
+          <t>Rank → 1→1 · Conf 57% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr"/>
       <c r="U16" s="3" t="n">
-        <v>21.5</v>
+        <v>56.8</v>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
@@ -2848,11 +2992,11 @@
         </is>
       </c>
       <c r="W16" s="3" t="n">
-        <v>-25.9</v>
+        <v>29.2</v>
       </c>
       <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>60</v>
@@ -2862,75 +3006,47 @@
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="AC16" s="3" t="n">
-        <v>2744.3</v>
-      </c>
-      <c r="AD16" s="3" t="n">
-        <v>2744.3</v>
-      </c>
-      <c r="AE16" s="3" t="n">
-        <v>2716.86</v>
-      </c>
-      <c r="AF16" s="3" t="n">
-        <v>2771.74</v>
-      </c>
-      <c r="AG16" s="3" t="n">
-        <v>2607.085</v>
-      </c>
-      <c r="AH16" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI16" s="3" t="n">
-        <v>2963.844000000001</v>
-      </c>
-      <c r="AJ16" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK16" s="3" t="n">
-        <v>3155.945</v>
-      </c>
-      <c r="AL16" s="3" t="n">
-        <v>15</v>
-      </c>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr"/>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr"/>
+      <c r="AF16" s="3" t="inlineStr"/>
+      <c r="AG16" s="3" t="inlineStr"/>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr"/>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr"/>
       <c r="AM16" s="3" t="n">
-        <v>2720</v>
+        <v>366.18</v>
       </c>
       <c r="AN16" s="3" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AO16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>2.23</v>
+      </c>
+      <c r="AO16" s="3" t="inlineStr"/>
+      <c r="AP16" s="3" t="inlineStr"/>
+      <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr"/>
       <c r="AS16" s="3" t="inlineStr"/>
       <c r="AT16" s="3" t="inlineStr"/>
-      <c r="AU16" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="AU16" s="3" t="inlineStr"/>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 00:46</t>
+          <t>2026-09-04 12:28</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>R1-LUPIN-IND-20260904-36ad50</t>
+          <t>R2-V-USA-20260810-1697f4</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>LUPIN_IND_20260904</t>
+          <t>V_USA_20260810</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2940,22 +3056,22 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>INDIA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Lupin</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -2966,10 +3082,10 @@
       <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="3" t="inlineStr"/>
       <c r="K17" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>0</v>
@@ -2981,12 +3097,12 @@
       <c r="R17" s="3" t="inlineStr"/>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 3→3 · Conf 72% · momentum → · 61d left · → HOLD</t>
+          <t>Rank → 2→2 · Conf 54% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr"/>
       <c r="U17" s="3" t="n">
-        <v>72</v>
+        <v>53.6</v>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
@@ -2994,11 +3110,11 @@
         </is>
       </c>
       <c r="W17" s="3" t="n">
-        <v>71</v>
+        <v>27.8</v>
       </c>
       <c r="X17" s="3" t="inlineStr"/>
       <c r="Y17" s="3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>60</v>
@@ -3006,786 +3122,42 @@
       <c r="AA17" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="AB17" s="3" t="inlineStr"/>
-      <c r="AC17" s="3" t="n">
-        <v>2417</v>
-      </c>
-      <c r="AD17" s="3" t="n">
-        <v>2417</v>
-      </c>
-      <c r="AE17" s="3" t="n">
-        <v>2392.83</v>
-      </c>
-      <c r="AF17" s="3" t="n">
-        <v>2441.17</v>
-      </c>
-      <c r="AG17" s="3" t="n">
-        <v>2296.15</v>
-      </c>
-      <c r="AH17" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI17" s="3" t="n">
-        <v>2610.36</v>
-      </c>
-      <c r="AJ17" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK17" s="3" t="n">
-        <v>2779.55</v>
-      </c>
-      <c r="AL17" s="3" t="n">
-        <v>15</v>
-      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr"/>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr"/>
+      <c r="AF17" s="3" t="inlineStr"/>
+      <c r="AG17" s="3" t="inlineStr"/>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr"/>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr"/>
       <c r="AM17" s="3" t="n">
-        <v>2155.2</v>
+        <v>378.4</v>
       </c>
       <c r="AN17" s="3" t="n">
-        <v>-1.08</v>
-      </c>
-      <c r="AO17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" s="3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ17" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>0.09</v>
+      </c>
+      <c r="AO17" s="3" t="inlineStr"/>
+      <c r="AP17" s="3" t="inlineStr"/>
+      <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr"/>
       <c r="AS17" s="3" t="inlineStr"/>
       <c r="AT17" s="3" t="inlineStr"/>
-      <c r="AU17" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="AU17" s="3" t="inlineStr"/>
       <c r="AV17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 00:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>R1-PIDILITIND-IND-20260904-2ebad5</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>PIDILITIND_IND_20260904</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>PIDILITIND</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Pidilite</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr"/>
-      <c r="J18" s="3" t="inlineStr"/>
-      <c r="K18" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="3" t="inlineStr"/>
-      <c r="O18" s="3" t="inlineStr"/>
-      <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="3" t="inlineStr"/>
-      <c r="R18" s="3" t="inlineStr"/>
-      <c r="S18" s="3" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 3→3 · Conf 87% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T18" s="3" t="inlineStr"/>
-      <c r="U18" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="V18" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W18" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="X18" s="3" t="inlineStr"/>
-      <c r="Y18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA18" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB18" s="3" t="inlineStr"/>
-      <c r="AC18" s="3" t="n">
-        <v>1625.5</v>
-      </c>
-      <c r="AD18" s="3" t="n">
-        <v>1625.5</v>
-      </c>
-      <c r="AE18" s="3" t="n">
-        <v>1609.24</v>
-      </c>
-      <c r="AF18" s="3" t="n">
-        <v>1641.76</v>
-      </c>
-      <c r="AG18" s="3" t="n">
-        <v>1544.225</v>
-      </c>
-      <c r="AH18" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI18" s="3" t="n">
-        <v>1755.54</v>
-      </c>
-      <c r="AJ18" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK18" s="3" t="n">
-        <v>1869.325</v>
-      </c>
-      <c r="AL18" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM18" s="3" t="n">
-        <v>1637</v>
-      </c>
-      <c r="AN18" s="3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AO18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" s="3" t="inlineStr"/>
-      <c r="AS18" s="3" t="inlineStr"/>
-      <c r="AT18" s="3" t="inlineStr"/>
-      <c r="AU18" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04 00:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>R1-KOTAKBANK-IND-20260904-0dc0b0</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>KOTAKBANK_IND_20260904</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>Kotak Bank</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr"/>
-      <c r="K19" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr"/>
-      <c r="P19" s="3" t="inlineStr"/>
-      <c r="Q19" s="3" t="inlineStr"/>
-      <c r="R19" s="3" t="inlineStr"/>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 5→5 · Conf 71% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T19" s="3" t="inlineStr"/>
-      <c r="U19" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="V19" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W19" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="X19" s="3" t="inlineStr"/>
-      <c r="Y19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA19" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB19" s="3" t="inlineStr"/>
-      <c r="AC19" s="3" t="n">
-        <v>389.3</v>
-      </c>
-      <c r="AD19" s="3" t="n">
-        <v>389.3</v>
-      </c>
-      <c r="AE19" s="3" t="n">
-        <v>385.41</v>
-      </c>
-      <c r="AF19" s="3" t="n">
-        <v>393.19</v>
-      </c>
-      <c r="AG19" s="3" t="n">
-        <v>369.835</v>
-      </c>
-      <c r="AH19" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI19" s="3" t="n">
-        <v>420.444</v>
-      </c>
-      <c r="AJ19" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK19" s="3" t="n">
-        <v>447.695</v>
-      </c>
-      <c r="AL19" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM19" s="3" t="n">
-        <v>423.5</v>
-      </c>
-      <c r="AN19" s="3" t="n">
-        <v>-0.55</v>
-      </c>
-      <c r="AO19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" s="3" t="inlineStr"/>
-      <c r="AS19" s="3" t="inlineStr"/>
-      <c r="AT19" s="3" t="inlineStr"/>
-      <c r="AU19" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV19" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04 00:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>R1-COALINDIA-IND-20260904-28ce0e</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>COALINDIA_IND_20260904</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>COALINDIA</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Coal India</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr"/>
-      <c r="K20" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="R20" s="3" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
-        </is>
-      </c>
-      <c r="S20" s="3" t="inlineStr">
-        <is>
-          <t>🟡 WAIT (Δ+1.1%) · Rank → 10→10 · Conf 66% · momentum → · band HOLD · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T20" s="3" t="inlineStr"/>
-      <c r="U20" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="V20" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W20" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="X20" s="3" t="inlineStr"/>
-      <c r="Y20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA20" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB20" s="3" t="inlineStr"/>
-      <c r="AC20" s="3" t="n">
-        <v>420.05</v>
-      </c>
-      <c r="AD20" s="3" t="n">
-        <v>411.3</v>
-      </c>
-      <c r="AE20" s="3" t="n">
-        <v>407.19</v>
-      </c>
-      <c r="AF20" s="3" t="n">
-        <v>415.41</v>
-      </c>
-      <c r="AG20" s="3" t="n">
-        <v>390.735</v>
-      </c>
-      <c r="AH20" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI20" s="3" t="n">
-        <v>444.2040000000001</v>
-      </c>
-      <c r="AJ20" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK20" s="3" t="n">
-        <v>472.995</v>
-      </c>
-      <c r="AL20" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM20" s="3" t="n">
-        <v>417.85</v>
-      </c>
-      <c r="AN20" s="3" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="AO20" s="3" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AP20" s="3" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AQ20" s="3" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="AR20" s="3" t="inlineStr"/>
-      <c r="AS20" s="3" t="inlineStr"/>
-      <c r="AT20" s="3" t="inlineStr"/>
-      <c r="AU20" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV20" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04 00:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>R1-BRITANNIA-IND-20260904-09998f</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>BRITANNIA_IND_20260904</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>BRITANNIA</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="3" t="inlineStr"/>
-      <c r="P21" s="3" t="inlineStr"/>
-      <c r="Q21" s="3" t="inlineStr"/>
-      <c r="R21" s="3" t="inlineStr"/>
-      <c r="S21" s="3" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 9→9 · Conf 66% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T21" s="3" t="inlineStr"/>
-      <c r="U21" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="V21" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W21" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="X21" s="3" t="inlineStr"/>
-      <c r="Y21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA21" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB21" s="3" t="inlineStr"/>
-      <c r="AC21" s="3" t="n">
-        <v>5406</v>
-      </c>
-      <c r="AD21" s="3" t="n">
-        <v>5406</v>
-      </c>
-      <c r="AE21" s="3" t="n">
-        <v>5351.94</v>
-      </c>
-      <c r="AF21" s="3" t="n">
-        <v>5460.06</v>
-      </c>
-      <c r="AG21" s="3" t="n">
-        <v>5135.7</v>
-      </c>
-      <c r="AH21" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI21" s="3" t="n">
-        <v>5838.48</v>
-      </c>
-      <c r="AJ21" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK21" s="3" t="n">
-        <v>6216.9</v>
-      </c>
-      <c r="AL21" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM21" s="3" t="n">
-        <v>5154</v>
-      </c>
-      <c r="AN21" s="3" t="n">
-        <v>-0.47</v>
-      </c>
-      <c r="AO21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" s="3" t="inlineStr"/>
-      <c r="AS21" s="3" t="inlineStr"/>
-      <c r="AT21" s="3" t="inlineStr"/>
-      <c r="AU21" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV21" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04 00:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>R1-TATAPOWER-IND-20260904-f6863d</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>TATAPOWER_IND_20260904</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>TATAPOWER</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Tata Power</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr"/>
-      <c r="J22" s="3" t="inlineStr"/>
-      <c r="K22" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3" t="inlineStr"/>
-      <c r="O22" s="3" t="inlineStr"/>
-      <c r="P22" s="3" t="inlineStr"/>
-      <c r="Q22" s="3" t="inlineStr"/>
-      <c r="R22" s="3" t="inlineStr"/>
-      <c r="S22" s="3" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 6→6 · Conf 64% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T22" s="3" t="inlineStr"/>
-      <c r="U22" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="V22" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W22" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="X22" s="3" t="inlineStr"/>
-      <c r="Y22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA22" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB22" s="3" t="inlineStr"/>
-      <c r="AC22" s="3" t="n">
-        <v>381.6</v>
-      </c>
-      <c r="AD22" s="3" t="n">
-        <v>381.6</v>
-      </c>
-      <c r="AE22" s="3" t="n">
-        <v>377.78</v>
-      </c>
-      <c r="AF22" s="3" t="n">
-        <v>385.42</v>
-      </c>
-      <c r="AG22" s="3" t="n">
-        <v>362.52</v>
-      </c>
-      <c r="AH22" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI22" s="3" t="n">
-        <v>412.128</v>
-      </c>
-      <c r="AJ22" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK22" s="3" t="n">
-        <v>438.84</v>
-      </c>
-      <c r="AL22" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM22" s="3" t="n">
-        <v>364</v>
-      </c>
-      <c r="AN22" s="3" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="AO22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR22" s="3" t="inlineStr"/>
-      <c r="AS22" s="3" t="inlineStr"/>
-      <c r="AT22" s="3" t="inlineStr"/>
-      <c r="AU22" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV22" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04 00:46</t>
+          <t>2026-09-04 12:28</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AV22"/>
+  <autoFilter ref="A1:AV17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_daily_2026-09-04.xlsx
+++ b/reports/telegram/aegis_daily_2026-09-04.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV17"/>
+  <dimension ref="A1:AV16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -764,18 +764,18 @@
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr"/>
       <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L2" s="3" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="3" t="n">
-        <v>76.7</v>
+        <v>73.8</v>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>50.6</v>
+        <v>50.8</v>
       </c>
       <c r="Q2" s="3" t="n">
         <v>-0.8</v>
@@ -795,12 +795,12 @@
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 51% · band HOLD · 17d left · → STRONG BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #6 · Conf 52% · band HOLD · 17d left · → HOLD</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr"/>
       <c r="U2" s="3" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="W2" s="3" t="n">
-        <v>33.8</v>
+        <v>30.2</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>1</v>
@@ -828,40 +828,40 @@
         </is>
       </c>
       <c r="AC2" s="3" t="n">
+        <v>178.2</v>
+      </c>
+      <c r="AD2" s="3" t="n">
+        <v>178.2</v>
+      </c>
+      <c r="AE2" s="3" t="n">
+        <v>176.42</v>
+      </c>
+      <c r="AF2" s="3" t="n">
+        <v>179.98</v>
+      </c>
+      <c r="AG2" s="3" t="n">
+        <v>169.29</v>
+      </c>
+      <c r="AH2" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI2" s="3" t="n">
+        <v>192.46</v>
+      </c>
+      <c r="AJ2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK2" s="3" t="n">
+        <v>204.93</v>
+      </c>
+      <c r="AL2" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM2" s="3" t="n">
         <v>182.53</v>
       </c>
-      <c r="AD2" s="3" t="n">
-        <v>182.53</v>
-      </c>
-      <c r="AE2" s="3" t="n">
-        <v>180.7</v>
-      </c>
-      <c r="AF2" s="3" t="n">
-        <v>184.36</v>
-      </c>
-      <c r="AG2" s="3" t="n">
-        <v>171.58</v>
-      </c>
-      <c r="AH2" s="3" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AI2" s="3" t="n">
-        <v>204.43</v>
-      </c>
-      <c r="AJ2" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK2" s="3" t="n">
-        <v>226.34</v>
-      </c>
-      <c r="AL2" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AM2" s="3" t="n">
-        <v>169.46</v>
-      </c>
       <c r="AN2" s="3" t="n">
-        <v>7.71</v>
+        <v>-2.37</v>
       </c>
       <c r="AO2" s="3" t="n">
         <v>0</v>
@@ -878,27 +878,25 @@
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr"/>
-      <c r="AT2" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="AT2" s="3" t="inlineStr"/>
       <c r="AU2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AV2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 12:28</t>
+          <t>2026-09-04 13:52</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>R2-COP-USA-20260904-01ae27</t>
+          <t>R2-ECL-USA-20260904-9e334f</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>COP_USA_20260904</t>
+          <t>ECL_USA_20260904</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -918,7 +916,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>ECL</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -929,44 +927,44 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>→ PLTR · +5.5pp alpha</t>
+          <t>→ INCY · +61.2pp alpha</t>
         </is>
       </c>
       <c r="J3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>52.7</v>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🔴</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>56.4</v>
+        <v>32.4</v>
       </c>
       <c r="Q3" s="3" t="n">
         <v>-0.8</v>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts · ECL avg-corr 0.24 to universe · adds diversification → +1.5pts</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank #6 · Conf 57% · band STRONG · 60d left · → EXIT (rotate to PLTR)</t>
+          <t>🔴 AVOID · Rank #11 · Conf 33% · band EXIT · 60d left · → EXIT (rotate to INCY)</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="n">
-        <v>57.1</v>
+        <v>33.1</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -974,7 +972,7 @@
         </is>
       </c>
       <c r="W3" s="3" t="n">
-        <v>28.3</v>
+        <v>-27</v>
       </c>
       <c r="X3" s="3" t="n">
         <v>1</v>
@@ -994,40 +992,40 @@
         </is>
       </c>
       <c r="AC3" s="3" t="n">
-        <v>135.72</v>
+        <v>277.69</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>135.72</v>
+        <v>277.69</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>134.36</v>
+        <v>274.91</v>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>137.08</v>
+        <v>280.47</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>128.93</v>
+        <v>263.81</v>
       </c>
       <c r="AH3" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>146.58</v>
+        <v>299.91</v>
       </c>
       <c r="AJ3" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>156.08</v>
+        <v>319.34</v>
       </c>
       <c r="AL3" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" s="3" t="n">
-        <v>137.2</v>
+        <v>278.97</v>
       </c>
       <c r="AN3" s="3" t="n">
-        <v>-1.08</v>
+        <v>-0.46</v>
       </c>
       <c r="AO3" s="3" t="inlineStr"/>
       <c r="AP3" s="3" t="n">
@@ -1038,29 +1036,29 @@
       </c>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Trend · Momentum · News</t>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr"/>
       <c r="AT3" s="3" t="inlineStr"/>
       <c r="AU3" s="3" t="n">
-        <v>5.49</v>
+        <v>61.22</v>
       </c>
       <c r="AV3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 12:28</t>
+          <t>2026-09-04 13:52</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>R2-PSX-USA-20260904-1d95f1</t>
+          <t>R2-J-USA-20260904-852009</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>PSX_USA_20260904</t>
+          <t>J_USA_20260904</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1080,7 +1078,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>J</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
@@ -1091,27 +1089,27 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>→ PLTR · +7.3pp alpha</t>
+          <t>→ INCY · +62.2pp alpha</t>
         </is>
       </c>
       <c r="J4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="3" t="n">
-        <v>77.09999999999999</v>
+        <v>52.7</v>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>🟢</t>
+          <t>🔴</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>50.6</v>
+        <v>32.4</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>-0.8</v>
@@ -1123,12 +1121,12 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank #10 · Conf 51% · band HOLD · 60d left · → EXIT (rotate to PLTR)</t>
+          <t>🔴 AVOID · Rank #12 · Conf 33% · band EXIT · 60d left · → EXIT (rotate to INCY)</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr"/>
       <c r="U4" s="3" t="n">
-        <v>51.4</v>
+        <v>33.1</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1136,7 +1134,7 @@
         </is>
       </c>
       <c r="W4" s="3" t="n">
-        <v>26.5</v>
+        <v>-28</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>1</v>
@@ -1156,40 +1154,40 @@
         </is>
       </c>
       <c r="AC4" s="3" t="n">
-        <v>254.66</v>
+        <v>145.01</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>254.66</v>
+        <v>145.01</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>252.11</v>
+        <v>143.56</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>257.21</v>
+        <v>146.46</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>241.93</v>
+        <v>137.76</v>
       </c>
       <c r="AH4" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>275.03</v>
+        <v>156.61</v>
       </c>
       <c r="AJ4" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>292.86</v>
+        <v>166.76</v>
       </c>
       <c r="AL4" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM4" s="3" t="n">
-        <v>256.09</v>
+        <v>147.54</v>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.71</v>
       </c>
       <c r="AO4" s="3" t="inlineStr"/>
       <c r="AP4" s="3" t="n">
@@ -1200,29 +1198,29 @@
       </c>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>Trend · Momentum · Growth</t>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr"/>
       <c r="AT4" s="3" t="inlineStr"/>
       <c r="AU4" s="3" t="n">
-        <v>7.33</v>
+        <v>62.21</v>
       </c>
       <c r="AV4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 12:28</t>
+          <t>2026-09-04 13:52</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>R2-TAP-USA-20260904-8b67a3</t>
+          <t>R1-PLTR-USA-20260904-ed7adc</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TAP_USA_20260904</t>
+          <t>PLTR_USA_20260904</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1237,43 +1235,37 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>TAP</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>→ PLTR · +60.0pp alpha</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="n">
-        <v>52.6</v>
+        <v>73.8</v>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>🔴</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
-        <v>30.2</v>
+        <v>50.8</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>-0.8</v>
@@ -1285,12 +1277,12 @@
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank #11 · Conf 31% · band EXIT · 60d left · → EXIT (rotate to PLTR)</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #1 · Conf 52% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="n">
-        <v>30.9</v>
+        <v>51.5</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
@@ -1298,81 +1290,79 @@
         </is>
       </c>
       <c r="W5" s="3" t="n">
-        <v>-26.1</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>68.7</v>
+      </c>
+      <c r="X5" s="3" t="inlineStr"/>
       <c r="Y5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA5" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB5" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AB5" s="3" t="inlineStr"/>
       <c r="AC5" s="3" t="n">
-        <v>40.57</v>
+        <v>178.2</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>40.57</v>
+        <v>178.2</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>40.16</v>
+        <v>174.64</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>40.98</v>
+        <v>181.76</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>38.54</v>
+        <v>169.29</v>
       </c>
       <c r="AH5" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>43.82</v>
+        <v>192.456</v>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>8.01</v>
+        <v>8</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>46.66</v>
+        <v>205.92792</v>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>15.01</v>
+        <v>15.56</v>
       </c>
       <c r="AM5" s="3" t="n">
-        <v>40.54</v>
+        <v>182.53</v>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AO5" s="3" t="inlineStr"/>
+        <v>-2.37</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AP5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR5" s="3" t="inlineStr">
-        <is>
-          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
-        </is>
-      </c>
-      <c r="AS5" s="3" t="inlineStr"/>
-      <c r="AT5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr"/>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU5" s="3" t="n">
-        <v>59.95</v>
+        <v>8</v>
       </c>
       <c r="AV5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 12:28</t>
+          <t>2026-09-04 13:52</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1406,12 @@
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" s="3" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="3" t="n">
-        <v>73.8</v>
+        <v>75.7</v>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
@@ -1441,12 +1431,12 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #1 · Conf 51% · momentum → · band HOLD · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 51% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr"/>
       <c r="U6" s="3" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
@@ -1454,7 +1444,7 @@
         </is>
       </c>
       <c r="W6" s="3" t="n">
-        <v>68.5</v>
+        <v>67.5</v>
       </c>
       <c r="X6" s="3" t="inlineStr"/>
       <c r="Y6" s="3" t="n">
@@ -1468,40 +1458,40 @@
       </c>
       <c r="AB6" s="3" t="inlineStr"/>
       <c r="AC6" s="3" t="n">
-        <v>958.16</v>
+        <v>993.77</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>958.16</v>
+        <v>993.77</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>939</v>
+        <v>983.83</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>977.3200000000001</v>
+        <v>1003.71</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>910.252</v>
+        <v>944.0814999999999</v>
       </c>
       <c r="AH6" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>1034.8128</v>
+        <v>1113.02</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>1107.249696</v>
+        <v>1190.9314</v>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>15.56</v>
+        <v>19.84</v>
       </c>
       <c r="AM6" s="3" t="n">
-        <v>956.08</v>
+        <v>958.16</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.22</v>
+        <v>3.72</v>
       </c>
       <c r="AO6" s="3" t="n">
         <v>0</v>
@@ -1522,23 +1512,23 @@
         <v>5</v>
       </c>
       <c r="AU6" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 12:28</t>
+          <t>2026-09-04 13:52</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>R1-PLTR-USA-20260904-ed7adc</t>
+          <t>R1-INCY-USA-20260904-e82d63</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>PLTR_USA_20260904</t>
+          <t>INCY_USA_20260904</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1558,7 +1548,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr"/>
@@ -1570,12 +1560,12 @@
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="n">
-        <v>76.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
@@ -1583,7 +1573,7 @@
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>50.6</v>
+        <v>53.6</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>-0.8</v>
@@ -1595,12 +1585,12 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 51% · momentum → · band HOLD · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #3 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="n">
-        <v>51.4</v>
+        <v>54.4</v>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
@@ -1608,7 +1598,7 @@
         </is>
       </c>
       <c r="W7" s="3" t="n">
-        <v>67.3</v>
+        <v>66</v>
       </c>
       <c r="X7" s="3" t="inlineStr"/>
       <c r="Y7" s="3" t="n">
@@ -1622,40 +1612,40 @@
       </c>
       <c r="AB7" s="3" t="inlineStr"/>
       <c r="AC7" s="3" t="n">
-        <v>182.53</v>
+        <v>126.89</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>182.53</v>
+        <v>126.89</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>180.7</v>
+        <v>125.63</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>184.36</v>
+        <v>128.16</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>173.4035</v>
+        <v>120.5455</v>
       </c>
       <c r="AH7" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>204.43</v>
+        <v>142.12</v>
       </c>
       <c r="AJ7" s="3" t="n">
         <v>12</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>218.7401</v>
+        <v>152.0684</v>
       </c>
       <c r="AL7" s="3" t="n">
         <v>19.84</v>
       </c>
       <c r="AM7" s="3" t="n">
-        <v>169.46</v>
+        <v>128</v>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>7.71</v>
+        <v>-0.86</v>
       </c>
       <c r="AO7" s="3" t="n">
         <v>0</v>
@@ -1680,19 +1670,19 @@
       </c>
       <c r="AV7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 12:28</t>
+          <t>2026-09-04 13:52</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>R1-INCY-USA-20260904-e82d63</t>
+          <t>R1-HOOD-USA-20260904-31b01c</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>INCY_USA_20260904</t>
+          <t>HOOD_USA_20260904</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1712,7 +1702,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr"/>
@@ -1724,12 +1714,12 @@
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="3" t="n">
-        <v>76</v>
+        <v>77.3</v>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
@@ -1737,7 +1727,7 @@
         </is>
       </c>
       <c r="P8" s="3" t="n">
-        <v>53.5</v>
+        <v>50.8</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>-0.8</v>
@@ -1749,12 +1739,12 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #3 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 52% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr"/>
       <c r="U8" s="3" t="n">
-        <v>54.2</v>
+        <v>51.5</v>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
@@ -1762,7 +1752,7 @@
         </is>
       </c>
       <c r="W8" s="3" t="n">
-        <v>66.5</v>
+        <v>61.1</v>
       </c>
       <c r="X8" s="3" t="inlineStr"/>
       <c r="Y8" s="3" t="n">
@@ -1776,40 +1766,40 @@
       </c>
       <c r="AB8" s="3" t="inlineStr"/>
       <c r="AC8" s="3" t="n">
-        <v>128</v>
+        <v>120.38</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>128</v>
+        <v>120.38</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>126.72</v>
+        <v>117.97</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>129.28</v>
+        <v>122.79</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>121.6</v>
+        <v>114.361</v>
       </c>
       <c r="AH8" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>143.36</v>
+        <v>130.0104</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>153.3952</v>
+        <v>139.111128</v>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>19.84</v>
+        <v>15.56</v>
       </c>
       <c r="AM8" s="3" t="n">
-        <v>128.83</v>
+        <v>124.72</v>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>-0.64</v>
+        <v>-3.48</v>
       </c>
       <c r="AO8" s="3" t="n">
         <v>0</v>
@@ -1830,23 +1820,23 @@
         <v>5</v>
       </c>
       <c r="AU8" s="3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AV8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 12:28</t>
+          <t>2026-09-04 13:52</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>R1-HOOD-USA-20260904-31b01c</t>
+          <t>R1-VLO-USA-20260904-c6a265</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>HOOD_USA_20260904</t>
+          <t>VLO_USA_20260904</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1866,7 +1856,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -1878,12 +1868,12 @@
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
@@ -1891,7 +1881,7 @@
         </is>
       </c>
       <c r="P9" s="3" t="n">
-        <v>50.6</v>
+        <v>56.4</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>-0.8</v>
@@ -1903,12 +1893,12 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 51% · momentum → · band HOLD · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #5 · Conf 57% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr"/>
       <c r="U9" s="3" t="n">
-        <v>51.4</v>
+        <v>57.2</v>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
@@ -1916,7 +1906,7 @@
         </is>
       </c>
       <c r="W9" s="3" t="n">
-        <v>60.9</v>
+        <v>58.6</v>
       </c>
       <c r="X9" s="3" t="inlineStr"/>
       <c r="Y9" s="3" t="n">
@@ -1930,40 +1920,40 @@
       </c>
       <c r="AB9" s="3" t="inlineStr"/>
       <c r="AC9" s="3" t="n">
-        <v>124.72</v>
+        <v>363.45</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>124.72</v>
+        <v>363.45</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>122.23</v>
+        <v>359.82</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>127.21</v>
+        <v>367.08</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>118.484</v>
+        <v>345.2775</v>
       </c>
       <c r="AH9" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>134.6976</v>
+        <v>407.06</v>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>144.126432</v>
+        <v>435.5542</v>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>15.56</v>
+        <v>19.84</v>
       </c>
       <c r="AM9" s="3" t="n">
-        <v>106.99</v>
+        <v>370.69</v>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>16.57</v>
+        <v>-1.95</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>0</v>
@@ -1984,23 +1974,23 @@
         <v>5</v>
       </c>
       <c r="AU9" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 12:28</t>
+          <t>2026-09-04 13:52</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>R1-VLO-USA-20260904-c6a265</t>
+          <t>R1-SMCI-USA-20260904-4dac15</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>VLO_USA_20260904</t>
+          <t>SMCI_USA_20260904</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -2020,7 +2010,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -2032,12 +2022,12 @@
       <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr"/>
       <c r="K10" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L10" s="3" t="inlineStr"/>
       <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
@@ -2045,7 +2035,7 @@
         </is>
       </c>
       <c r="P10" s="3" t="n">
-        <v>56.4</v>
+        <v>53.6</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>-0.8</v>
@@ -2057,12 +2047,12 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #5 · Conf 57% · momentum → · band STRONG · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.9%) · Rank #6 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr"/>
       <c r="U10" s="3" t="n">
-        <v>57.1</v>
+        <v>54.4</v>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
@@ -2070,7 +2060,7 @@
         </is>
       </c>
       <c r="W10" s="3" t="n">
-        <v>58.6</v>
+        <v>56.1</v>
       </c>
       <c r="X10" s="3" t="inlineStr"/>
       <c r="Y10" s="3" t="n">
@@ -2084,40 +2074,40 @@
       </c>
       <c r="AB10" s="3" t="inlineStr"/>
       <c r="AC10" s="3" t="n">
-        <v>370.69</v>
+        <v>38.72</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>370.69</v>
+        <v>38.72</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>366.98</v>
+        <v>37.95</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>374.4</v>
+        <v>39.49</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>352.1555</v>
+        <v>36.784</v>
       </c>
       <c r="AH10" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>415.17</v>
+        <v>41.8176</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>444.2319000000001</v>
+        <v>44.744832</v>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>19.84</v>
+        <v>15.56</v>
       </c>
       <c r="AM10" s="3" t="n">
-        <v>366.09</v>
+        <v>37.87</v>
       </c>
       <c r="AN10" s="3" t="n">
-        <v>1.26</v>
+        <v>2.24</v>
       </c>
       <c r="AO10" s="3" t="n">
         <v>0</v>
@@ -2138,23 +2128,23 @@
         <v>5</v>
       </c>
       <c r="AU10" s="3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AV10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 12:28</t>
+          <t>2026-09-04 13:52</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>R1-GRMN-USA-20260904-66577b</t>
+          <t>R1-SNDK-USA-20260904-24e6db</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>GRMN_USA_20260904</t>
+          <t>SNDK_USA_20260904</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -2174,24 +2164,24 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L11" s="3" t="inlineStr"/>
       <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
@@ -2199,7 +2189,7 @@
         </is>
       </c>
       <c r="P11" s="3" t="n">
-        <v>53.4</v>
+        <v>44.8</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>-0.8</v>
@@ -2211,12 +2201,12 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #6 · Conf 54% · momentum → · band HOLD · 91d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 46% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr"/>
       <c r="U11" s="3" t="n">
-        <v>54.1</v>
+        <v>45.5</v>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
@@ -2224,7 +2214,7 @@
         </is>
       </c>
       <c r="W11" s="3" t="n">
-        <v>47.7</v>
+        <v>51</v>
       </c>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="n">
@@ -2238,40 +2228,40 @@
       </c>
       <c r="AB11" s="3" t="inlineStr"/>
       <c r="AC11" s="3" t="n">
-        <v>277.18</v>
+        <v>1643.12</v>
       </c>
       <c r="AD11" s="3" t="n">
-        <v>277.18</v>
+        <v>1643.12</v>
       </c>
       <c r="AE11" s="3" t="n">
-        <v>271.64</v>
+        <v>1610.26</v>
       </c>
       <c r="AF11" s="3" t="n">
-        <v>282.72</v>
+        <v>1675.98</v>
       </c>
       <c r="AG11" s="3" t="n">
-        <v>263.321</v>
+        <v>1560.964</v>
       </c>
       <c r="AH11" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>299.3544000000001</v>
+        <v>1774.5696</v>
       </c>
       <c r="AJ11" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>320.3092080000001</v>
+        <v>1898.789472</v>
       </c>
       <c r="AL11" s="3" t="n">
         <v>15.56</v>
       </c>
       <c r="AM11" s="3" t="n">
-        <v>276.04</v>
+        <v>1554.99</v>
       </c>
       <c r="AN11" s="3" t="n">
-        <v>0.41</v>
+        <v>5.67</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>0</v>
@@ -2296,19 +2286,19 @@
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 12:28</t>
+          <t>2026-09-04 13:52</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>R1-GDDY-USA-20260904-9a4122</t>
+          <t>R1-GRMN-USA-20260904-66577b</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>GDDY_USA_20260904</t>
+          <t>GRMN_USA_20260904</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -2328,7 +2318,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -2340,12 +2330,12 @@
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr"/>
       <c r="K12" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L12" s="3" t="inlineStr"/>
       <c r="M12" s="3" t="inlineStr"/>
       <c r="N12" s="3" t="n">
-        <v>83.3</v>
+        <v>71</v>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
@@ -2353,7 +2343,7 @@
         </is>
       </c>
       <c r="P12" s="3" t="n">
-        <v>53.5</v>
+        <v>53.4</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>-0.8</v>
@@ -2365,7 +2355,7 @@
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 54% · momentum → · band STRONG · 91d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 54% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr"/>
@@ -2378,7 +2368,7 @@
         </is>
       </c>
       <c r="W12" s="3" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="X12" s="3" t="inlineStr"/>
       <c r="Y12" s="3" t="n">
@@ -2392,40 +2382,40 @@
       </c>
       <c r="AB12" s="3" t="inlineStr"/>
       <c r="AC12" s="3" t="n">
-        <v>103.63</v>
+        <v>277.21</v>
       </c>
       <c r="AD12" s="3" t="n">
-        <v>103.63</v>
+        <v>277.21</v>
       </c>
       <c r="AE12" s="3" t="n">
-        <v>101.56</v>
+        <v>271.67</v>
       </c>
       <c r="AF12" s="3" t="n">
-        <v>105.7</v>
+        <v>282.75</v>
       </c>
       <c r="AG12" s="3" t="n">
-        <v>98.4485</v>
+        <v>263.3495</v>
       </c>
       <c r="AH12" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>111.9204</v>
+        <v>299.3868</v>
       </c>
       <c r="AJ12" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>119.754828</v>
+        <v>320.343876</v>
       </c>
       <c r="AL12" s="3" t="n">
         <v>15.56</v>
       </c>
       <c r="AM12" s="3" t="n">
-        <v>101.87</v>
+        <v>277.18</v>
       </c>
       <c r="AN12" s="3" t="n">
-        <v>1.73</v>
+        <v>0.01</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>0</v>
@@ -2450,19 +2440,19 @@
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 12:28</t>
+          <t>2026-09-04 13:52</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>R1-CRM-USA-20260904-7dc69e</t>
+          <t>R1-UBER-USA-20260904-a843ae</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CRM_USA_20260904</t>
+          <t>UBER_USA_20260904</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -2482,14 +2472,10 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2498,12 +2484,12 @@
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L13" s="3" t="inlineStr"/>
       <c r="M13" s="3" t="inlineStr"/>
       <c r="N13" s="3" t="n">
-        <v>79.5</v>
+        <v>71.2</v>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
@@ -2511,7 +2497,7 @@
         </is>
       </c>
       <c r="P13" s="3" t="n">
-        <v>53.4</v>
+        <v>53.6</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>-0.8</v>
@@ -2523,12 +2509,12 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 54% · momentum → · band HOLD · 91d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 54% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr"/>
       <c r="U13" s="3" t="n">
-        <v>54.1</v>
+        <v>54.4</v>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
@@ -2536,7 +2522,7 @@
         </is>
       </c>
       <c r="W13" s="3" t="n">
-        <v>36.4</v>
+        <v>46.7</v>
       </c>
       <c r="X13" s="3" t="inlineStr"/>
       <c r="Y13" s="3" t="n">
@@ -2550,40 +2536,40 @@
       </c>
       <c r="AB13" s="3" t="inlineStr"/>
       <c r="AC13" s="3" t="n">
-        <v>264.43</v>
+        <v>76.44</v>
       </c>
       <c r="AD13" s="3" t="n">
-        <v>264.43</v>
+        <v>76.44</v>
       </c>
       <c r="AE13" s="3" t="n">
-        <v>259.14</v>
+        <v>74.91</v>
       </c>
       <c r="AF13" s="3" t="n">
-        <v>269.72</v>
+        <v>77.97</v>
       </c>
       <c r="AG13" s="3" t="n">
-        <v>251.2085</v>
+        <v>72.61799999999999</v>
       </c>
       <c r="AH13" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>285.5844</v>
+        <v>82.5552</v>
       </c>
       <c r="AJ13" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>305.5753080000001</v>
+        <v>88.334064</v>
       </c>
       <c r="AL13" s="3" t="n">
         <v>15.56</v>
       </c>
       <c r="AM13" s="3" t="n">
-        <v>256.93</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="AN13" s="3" t="n">
-        <v>2.92</v>
+        <v>0.63</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>0</v>
@@ -2608,19 +2594,19 @@
       </c>
       <c r="AV13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 12:28</t>
+          <t>2026-09-04 13:52</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>R1-PSX-USA-20260904-b831e4</t>
+          <t>R1-GDDY-USA-20260904-9a4122</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PSX_USA_20260904</t>
+          <t>GDDY_USA_20260904</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2640,7 +2626,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -2652,12 +2638,12 @@
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr"/>
       <c r="K14" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L14" s="3" t="inlineStr"/>
       <c r="M14" s="3" t="inlineStr"/>
       <c r="N14" s="3" t="n">
-        <v>77.09999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
@@ -2665,7 +2651,7 @@
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>50.6</v>
+        <v>50.8</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>-0.8</v>
@@ -2677,12 +2663,12 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 51% · momentum → · band HOLD · 91d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 52% · momentum → · band STRONG · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr"/>
       <c r="U14" s="3" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
@@ -2690,7 +2676,7 @@
         </is>
       </c>
       <c r="W14" s="3" t="n">
-        <v>36</v>
+        <v>40.4</v>
       </c>
       <c r="X14" s="3" t="inlineStr"/>
       <c r="Y14" s="3" t="n">
@@ -2704,40 +2690,40 @@
       </c>
       <c r="AB14" s="3" t="inlineStr"/>
       <c r="AC14" s="3" t="n">
-        <v>254.66</v>
+        <v>101.02</v>
       </c>
       <c r="AD14" s="3" t="n">
-        <v>254.66</v>
+        <v>101.02</v>
       </c>
       <c r="AE14" s="3" t="n">
-        <v>249.57</v>
+        <v>99</v>
       </c>
       <c r="AF14" s="3" t="n">
-        <v>259.75</v>
+        <v>103.04</v>
       </c>
       <c r="AG14" s="3" t="n">
-        <v>241.927</v>
+        <v>95.96899999999999</v>
       </c>
       <c r="AH14" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>275.0328</v>
+        <v>109.1016</v>
       </c>
       <c r="AJ14" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>294.285096</v>
+        <v>116.738712</v>
       </c>
       <c r="AL14" s="3" t="n">
         <v>15.56</v>
       </c>
       <c r="AM14" s="3" t="n">
-        <v>256.09</v>
+        <v>103.63</v>
       </c>
       <c r="AN14" s="3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-2.52</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>0</v>
@@ -2762,19 +2748,19 @@
       </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 12:28</t>
+          <t>2026-09-04 13:52</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>R1-COP-USA-20260904-e63c2d</t>
+          <t>R2-TRV-USA-20260810-a2c57b</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>COP_USA_20260904</t>
+          <t>TRV_USA_20260810</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2789,15 +2775,19 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>COP</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2806,37 +2796,27 @@
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="inlineStr"/>
       <c r="K15" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr"/>
-      <c r="N15" s="3" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="Q15" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 0d (high) (+35 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr"/>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 57% · momentum → · band STRONG · 91d left · → HOLD</t>
+          <t>Rank → 1→1 · Conf 57% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr"/>
       <c r="U15" s="3" t="n">
-        <v>57.1</v>
+        <v>56.8</v>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
@@ -2844,91 +2824,61 @@
         </is>
       </c>
       <c r="W15" s="3" t="n">
-        <v>36</v>
+        <v>29.2</v>
       </c>
       <c r="X15" s="3" t="inlineStr"/>
       <c r="Y15" s="3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AA15" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB15" s="3" t="inlineStr"/>
-      <c r="AC15" s="3" t="n">
-        <v>135.72</v>
-      </c>
-      <c r="AD15" s="3" t="n">
-        <v>135.72</v>
-      </c>
-      <c r="AE15" s="3" t="n">
-        <v>133.01</v>
-      </c>
-      <c r="AF15" s="3" t="n">
-        <v>138.43</v>
-      </c>
-      <c r="AG15" s="3" t="n">
-        <v>128.934</v>
-      </c>
-      <c r="AH15" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI15" s="3" t="n">
-        <v>146.5776</v>
-      </c>
-      <c r="AJ15" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK15" s="3" t="n">
-        <v>156.838032</v>
-      </c>
-      <c r="AL15" s="3" t="n">
-        <v>15.56</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr"/>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr"/>
+      <c r="AF15" s="3" t="inlineStr"/>
+      <c r="AG15" s="3" t="inlineStr"/>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr"/>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr"/>
       <c r="AM15" s="3" t="n">
-        <v>137.2</v>
+        <v>374.34</v>
       </c>
       <c r="AN15" s="3" t="n">
-        <v>-1.08</v>
-      </c>
-      <c r="AO15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.11</v>
+      </c>
+      <c r="AO15" s="3" t="inlineStr"/>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr"/>
-      <c r="AS15" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AT15" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU15" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="AS15" s="3" t="inlineStr"/>
+      <c r="AT15" s="3" t="inlineStr"/>
+      <c r="AU15" s="3" t="inlineStr"/>
       <c r="AV15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 12:28</t>
+          <t>2026-09-04 13:52</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>R2-TRV-USA-20260810-a2c57b</t>
+          <t>R2-V-USA-20260810-1697f4</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>TRV_USA_20260810</t>
+          <t>V_USA_20260810</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2948,12 +2898,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -2964,10 +2914,10 @@
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>0</v>
@@ -2979,12 +2929,12 @@
       <c r="R16" s="3" t="inlineStr"/>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>Rank → 1→1 · Conf 57% · momentum → · 61d left · → HOLD</t>
+          <t>Rank → 2→2 · Conf 54% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr"/>
       <c r="U16" s="3" t="n">
-        <v>56.8</v>
+        <v>53.6</v>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
@@ -2992,7 +2942,7 @@
         </is>
       </c>
       <c r="W16" s="3" t="n">
-        <v>29.2</v>
+        <v>27.8</v>
       </c>
       <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
@@ -3020,10 +2970,10 @@
       <c r="AK16" s="3" t="inlineStr"/>
       <c r="AL16" s="3" t="inlineStr"/>
       <c r="AM16" s="3" t="n">
-        <v>366.18</v>
+        <v>378.75</v>
       </c>
       <c r="AN16" s="3" t="n">
-        <v>2.23</v>
+        <v>-0.66</v>
       </c>
       <c r="AO16" s="3" t="inlineStr"/>
       <c r="AP16" s="3" t="inlineStr"/>
@@ -3034,130 +2984,12 @@
       <c r="AU16" s="3" t="inlineStr"/>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04 12:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>R2-V-USA-20260810-1697f4</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>V_USA_20260810</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr"/>
-      <c r="J17" s="3" t="inlineStr"/>
-      <c r="K17" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="3" t="inlineStr"/>
-      <c r="O17" s="3" t="inlineStr"/>
-      <c r="P17" s="3" t="inlineStr"/>
-      <c r="Q17" s="3" t="inlineStr"/>
-      <c r="R17" s="3" t="inlineStr"/>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
-          <t>Rank → 2→2 · Conf 54% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T17" s="3" t="inlineStr"/>
-      <c r="U17" s="3" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="V17" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W17" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="X17" s="3" t="inlineStr"/>
-      <c r="Y17" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z17" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA17" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB17" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AC17" s="3" t="inlineStr"/>
-      <c r="AD17" s="3" t="inlineStr"/>
-      <c r="AE17" s="3" t="inlineStr"/>
-      <c r="AF17" s="3" t="inlineStr"/>
-      <c r="AG17" s="3" t="inlineStr"/>
-      <c r="AH17" s="3" t="inlineStr"/>
-      <c r="AI17" s="3" t="inlineStr"/>
-      <c r="AJ17" s="3" t="inlineStr"/>
-      <c r="AK17" s="3" t="inlineStr"/>
-      <c r="AL17" s="3" t="inlineStr"/>
-      <c r="AM17" s="3" t="n">
-        <v>378.4</v>
-      </c>
-      <c r="AN17" s="3" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AO17" s="3" t="inlineStr"/>
-      <c r="AP17" s="3" t="inlineStr"/>
-      <c r="AQ17" s="3" t="inlineStr"/>
-      <c r="AR17" s="3" t="inlineStr"/>
-      <c r="AS17" s="3" t="inlineStr"/>
-      <c r="AT17" s="3" t="inlineStr"/>
-      <c r="AU17" s="3" t="inlineStr"/>
-      <c r="AV17" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04 12:28</t>
+          <t>2026-09-04 13:52</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AV17"/>
+  <autoFilter ref="A1:AV16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>